--- a/data-raw/xlsx/tabla_advertencias.xlsx
+++ b/data-raw/xlsx/tabla_advertencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fernando_gallegos\Proyectos\odsa.eusilc\data-raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3E08DF-E3F6-40AA-86D3-18AEFF991391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067359E0-1FE3-4BC2-ACA9-BD2BF23715A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="188">
   <si>
     <t>id_advertencia</t>
   </si>
@@ -566,6 +566,24 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>Examinación manual</t>
+  </si>
+  <si>
+    <t>ingresos_netos_de</t>
+  </si>
+  <si>
+    <t>PYXXXN (?)</t>
+  </si>
+  <si>
+    <t>Alemania no reporta variables de ingreso neto (todas?)</t>
+  </si>
+  <si>
+    <t>La mayor parte de las variables de ingreso quedan ausentes</t>
+  </si>
+  <si>
+    <t>El paquete deja los ingresos ausentes</t>
   </si>
 </sst>
 </file>
@@ -918,8 +936,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3578,7 +3599,7 @@
         <v>162</v>
       </c>
       <c r="L70" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3807,6 +3828,44 @@
       </c>
       <c r="L76" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>183</v>
+      </c>
+      <c r="B77">
+        <v>2014</v>
+      </c>
+      <c r="C77">
+        <v>2019</v>
+      </c>
+      <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" t="s">
+        <v>184</v>
+      </c>
+      <c r="H77" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" t="s">
+        <v>185</v>
+      </c>
+      <c r="J77" t="s">
+        <v>186</v>
+      </c>
+      <c r="K77" t="s">
+        <v>187</v>
+      </c>
+      <c r="L77" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
